--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
+++ b/StructureDefinition-SEEHDSDiagnosticReportLab.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1157,6 +1157,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -1176,6 +1179,16 @@
   </si>
   <si>
     <t>Kliniskt relevant tidpunkt (härledd; specimen.timestamp → Specimen.collection.collectedDateTime)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.effective[x]:effectivePeriod</t>
+  </si>
+  <si>
+    <t>effectivePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -1829,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN65"/>
+  <dimension ref="A1:AN66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.1796875" customWidth="true" bestFit="true"/>
@@ -7183,7 +7196,7 @@
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>116</v>
+        <v>364</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>356</v>
@@ -7201,27 +7214,27 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>357</v>
@@ -7246,7 +7259,7 @@
         <v>261</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M48" t="s" s="2">
         <v>360</v>
@@ -7319,28 +7332,30 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7350,7 +7365,7 @@
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
@@ -7359,19 +7374,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>125</v>
+        <v>374</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7420,7 +7435,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7435,35 +7450,35 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>379</v>
+        <v>368</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>90</v>
@@ -7475,19 +7490,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>125</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7524,25 +7539,25 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -7551,30 +7566,28 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>389</v>
+        <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7584,7 +7597,7 @@
         <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
@@ -7593,19 +7606,19 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7642,19 +7655,19 @@
         <v>80</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>80</v>
+        <v>391</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7669,28 +7682,30 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="B52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7709,19 +7724,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7758,19 +7773,19 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7785,30 +7800,28 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7827,19 +7840,19 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7876,19 +7889,19 @@
         <v>80</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>80</v>
+        <v>407</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7903,28 +7916,30 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7934,28 +7949,28 @@
         <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="O54" t="s" s="2">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8004,7 +8019,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8019,28 +8034,28 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>80</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>418</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8059,19 +8074,19 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8120,7 +8135,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8138,25 +8153,25 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>425</v>
+        <v>343</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8166,7 +8181,7 @@
         <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -8175,18 +8190,20 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8234,7 +8251,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8252,10 +8269,10 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8263,14 +8280,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8286,21 +8303,21 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>437</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8348,7 +8365,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8366,10 +8383,10 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -8377,21 +8394,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>437</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8400,19 +8417,21 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>103</v>
+        <v>438</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>104</v>
+        <v>439</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>105</v>
+        <v>440</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8460,28 +8479,28 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>107</v>
+        <v>429</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8489,21 +8508,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8515,17 +8534,15 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8574,19 +8591,19 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
@@ -8603,14 +8620,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>442</v>
+        <v>109</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8623,26 +8640,24 @@
         <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>443</v>
+        <v>111</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>444</v>
+        <v>112</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O60" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8690,7 +8705,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>445</v>
+        <v>117</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8711,7 +8726,7 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -8719,33 +8734,33 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>80</v>
+        <v>446</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>447</v>
@@ -8754,10 +8769,10 @@
         <v>448</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>449</v>
+        <v>113</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>450</v>
+        <v>276</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -8806,19 +8821,19 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
@@ -8827,7 +8842,7 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>451</v>
+        <v>188</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -8835,10 +8850,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8846,7 +8861,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -8858,19 +8873,23 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -8918,10 +8937,10 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>89</v>
@@ -8939,52 +8958,50 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>458</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>457</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9032,10 +9049,10 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>89</v>
@@ -9050,35 +9067,35 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>462</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>80</v>
+        <v>462</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -9087,16 +9104,18 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>246</v>
+        <v>103</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9120,13 +9139,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>467</v>
+        <v>80</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9144,13 +9163,13 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
@@ -9162,10 +9181,10 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -9173,10 +9192,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9199,20 +9218,16 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>471</v>
+        <v>246</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9236,13 +9251,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>80</v>
+        <v>471</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9260,7 +9275,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9278,17 +9293,133 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN65">
+  <autoFilter ref="A1:AN66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9298,7 +9429,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
